--- a/aq_files/0066.xlsx
+++ b/aq_files/0066.xlsx
@@ -1,98 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>A jar contains 6 red and 4 blue marbles. Two marbles are drawn one after another with replacement. What is the probability that both are red?</t>
-  </si>
-  <si>
-    <t>A bag contains 5 green and 7 yellow balls. Two balls are drawn without replacement. What is the probability that both are yellow?</t>
-  </si>
-  <si>
-    <t>A box has 3 defective and 9 non-defective bulbs. Two bulbs are selected with replacement. Find the probability that both are defective.</t>
-  </si>
-  <si>
-    <t>From a deck of 52 playing cards, two cards are drawn without replacement. What is the probability that both are aces?</t>
-  </si>
-  <si>
-    <t>A bowl contains 8 chocolates and 2 candies. If two items are picked with replacement, what is the probability that both are chocolates?</t>
-  </si>
-  <si>
-    <t>A class has 10 boys and 15 girls. Two students are selected without replacement. What is the probability that both are girls?</t>
-  </si>
-  <si>
-    <t>A box contains 4 white, 5 black, and 1 red ball. Two balls are drawn with replacement. Find the probability of getting one white and one red (in any order).</t>
-  </si>
-  <si>
-    <t>A jar contains 3 blue, 3 green, and 4 yellow marbles. Two marbles are drawn without replacement. What is the probability that both are green?</t>
-  </si>
-  <si>
-    <t>A lottery drum has 20 tickets numbered 1 to 20. Two tickets are drawn with replacement. What is the probability that both are even numbers?</t>
-  </si>
-  <si>
-    <t>A basket contains 6 apples and 4 oranges. Two fruits are picked without replacement. What is the probability that both are apples?</t>
-  </si>
-  <si>
-    <t>A bag has 2 red, 3 blue, and 5 green balls. Two balls are drawn with replacement. What is the probability that both are of the same color?</t>
-  </si>
-  <si>
-    <t>A library shelf has 8 math books and 12 science books. Two books are selected without replacement. What is the probability that both are science books?</t>
-  </si>
-  <si>
-    <t>A jar contains 5 coins of ₹1 and 5 coins of ₹2. Two coins are drawn with replacement. What is the probability that both are ₹2 coins?</t>
-  </si>
-  <si>
-    <t>From a group of 7 men and 3 women, two people are selected without replacement. What is the probability that both are men?</t>
-  </si>
-  <si>
-    <t>A box contains 10 bulbs, 3 of which are defective. Two bulbs are selected with replacement. What is the probability that exactly one is defective?</t>
-  </si>
-  <si>
-    <t>A set of 12 cards numbered 1–12 is given. Two cards are drawn without replacement. What is the probability that both numbers are greater than 6?</t>
-  </si>
-  <si>
-    <t>A jar contains 4 red and 6 blue balls. Two balls are drawn with replacement. What is the probability that at least one is red?</t>
-  </si>
-  <si>
-    <t>A bag contains 9 balls, 4 of which are black. Two balls are drawn without replacement. What is the probability that none are black?</t>
-  </si>
-  <si>
-    <t>A drawer contains 5 pairs of socks (10 individual socks). Two socks are picked with replacement. What is the probability both are from the same pair?</t>
-  </si>
-  <si>
-    <t>A box has 6 pens and 4 pencils. Two items are chosen without replacement. What is the probability that one is a pen and the other is a pencil?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -102,29 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -322,113 +316,1123 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Record_ID,Timestamp,User_ID,User_Location,User_Device,User_OS,Session_ID,Page_URL,Page_Category,Action_Type,Action_Duration_Sec,Data_Size_KB,Response_Time_Ms,Server_ID,Server_Location,Data_Center,Data_Type,Processing_Time_Sec,Storage_Type,Compression_Ratio,Data_Format,Partition_Key,Batch_ID,Stream_Source,Latency_Ms,Throughput_MBps,Error_Code,Retry_Count,Data_Quality_Score,Processing_Node</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>BD-001,2024-03-01 00:00:01,USR-10001,New York,Desktop,Windows,SESS-001,https://site.com/home,Homepage,view,45,1250,234,SVR-101,New York,US-East,Structured,0.45,SSD,3.2,Parquet,2024-03-01,BATCH-001,Web_Log,12,450,NULL,0,98,Node-A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>BD-002,2024-03-01 00:00:02,USR-10002,Los Angeles,Mobile,iOS,SESS-002,https://site.com/product,Product,click,12,85,156,SVR-102,Los Angeles,US-West,Semi-structured,0.12,SSD,2.8,JSON,2024-03-01,BATCH-001,Mobile_App,8,320,NULL,0,95,Node-A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>BD-003,2024-03-01 00:00:03,USR-10003,Chicago,Tablet,Android,SESS-003,https://site.com/search,Search,search,8,210,189,SVR-103,Chicago,US-Central,Structured,0.23,HDD,1.5,Avro,2024-03-01,BATCH-001,Web_Log,15,280,NULL,0,92,Node-A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BD-004,2024-03-01 00:00:04,USR-10004,Houston,Desktop,Linux,SESS-004,https://site.com/cart,Cart,add_item,23,560,312,SVR-104,Houston,US-South,Structured,0.34,SSD,2.2,Parquet,2024-03-01,BATCH-001,Web_Log,18,390,NULL,0,96,Node-A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>BD-005,2024-03-01 00:00:05,USR-10005,Phoenix,Mobile,Android,SESS-005,https://site.com/checkout,Checkout,purchase,67,890,456,SVR-105,Phoenix,US-West,Semi-structured,0.56,SSD,3.0,JSON,2024-03-01,BATCH-001,Mobile_App,22,410,NULL,0,99,Node-A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>BD-006,2024-03-01 00:00:06,USR-10006,Philadelphia,Desktop,Windows,SESS-006,https://site.com/home,Homepage,view,34,980,278,SVR-101,New York,US-East,Structured,0.41,HDD,1.8,CSV,2024-03-01,BATCH-001,Web_Log,14,360,404,1,88,Node-A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>BD-007,2024-03-01 00:00:07,USR-10007,San Antonio,Tablet,iOS,SESS-007,https://site.com/product,Product,scroll,56,234,167,SVR-106,San Antonio,US-South,Semi-structured,0.19,SSD,2.5,JSON,2024-03-01,BATCH-002,Mobile_App,9,340,NULL,0,94,Node-A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>BD-008,2024-03-01 00:00:08,USR-10008,San Diego,Desktop,Linux,SESS-008,https://site.com/review,Review,submit,78,1250,567,SVR-107,San Diego,US-West,Unstructured,0.67,SSD,3.5,Text,2024-03-01,BATCH-002,Web_Log,25,520,NULL,0,97,Node-A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>BD-009,2024-03-01 00:00:09,USR-10009,Dallas,Mobile,iOS,SESS-009,https://site.com/cart,Cart,remove_item,15,45,98,SVR-108,Dallas,US-South,Structured,0.08,SSD,2.0,Parquet,2024-03-01,BATCH-002,Mobile_App,5,180,NULL,0,93,Node-A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>BD-010,2024-03-01 00:00:10,USR-10010,Austin,Desktop,Windows,SESS-010,https://site.com/login,Login,login,28,120,145,SVR-109,Austin,US-Central,Structured,0.15,HDD,1.2,CSV,2024-03-01,BATCH-002,Web_Log,11,210,401,1,85,Node-A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>BD-011,2024-03-01 00:00:11,USR-10011,San Jose,Mobile,Android,SESS-011,https://site.com/search,Search,search,9,340,234,SVR-110,San Jose,US-West,Semi-structured,0.21,SSD,2.7,JSON,2024-03-01,BATCH-002,Mobile_App,16,430,NULL,0,96,Node-A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>BD-012,2024-03-01 00:00:12,USR-10012,Jacksonville,Tablet,iOS,SESS-012,https://site.com/home,Homepage,view,41,1120,389,SVR-101,New York,US-East,Structured,0.52,SSD,3.1,Parquet,2024-03-01,BATCH-003,Web_Log,20,470,NULL,0,98,Node-A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>BD-013,2024-03-01 00:00:13,USR-10013,Indianapolis,Desktop,Linux,SESS-013,https://site.com/product,Product,share,34,670,345,SVR-112,Indianapolis,US-Central,Structured,0.38,HDD,1.6,Avro,2024-03-01,BATCH-003,Web_Log,17,400,NULL,0,91,Node-A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>BD-014,2024-03-01 00:00:14,USR-10014,San Francisco,Mobile,iOS,SESS-014,https://site.com/cart,Cart,checkout,89,1240,678,SVR-113,San Francisco,US-West,Semi-structured,0.71,SSD,3.4,JSON,2024-03-01,BATCH-003,Mobile_App,28,550,NULL,0,99,Node-A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>BD-015,2024-03-01 00:00:15,USR-10015,Columbus,Desktop,Windows,SESS-015,https://site.com/review,Review,view,22,230,156,SVR-114,Columbus,US-Central,Structured,0.18,SSD,2.1,Parquet,2024-03-01,BATCH-003,Web_Log,13,290,NULL,0,94,Node-A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>BD-016,2024-03-01 00:00:16,USR-10016,Fort Worth,Tablet,Android,SESS-016,https://site.com/home,Homepage,view,38,890,267,SVR-115,Fort Worth,US-South,Structured,0.44,HDD,1.4,CSV,2024-03-01,BATCH-003,Web_Log,19,380,500,2,86,Node-A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>BD-017,2024-03-01 00:00:17,USR-10017,Charlotte,Mobile,iOS,SESS-017,https://site.com/search,Search,search,12,450,278,SVR-116,Charlotte,US-East,Semi-structured,0.27,SSD,2.9,JSON,2024-03-01,BATCH-003,Mobile_App,14,360,NULL,0,95,Node-A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>BD-018,2024-03-01 00:00:18,USR-10018,Detroit,Desktop,Linux,SESS-018,https://site.com/product,Product,click,19,78,123,SVR-117,Detroit,US-Central,Structured,0.11,SSD,2.2,Parquet,2024-03-01,BATCH-004,Web_Log,7,220,NULL,0,92,Node-A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>BD-019,2024-03-01 00:00:19,USR-10019,El Paso,Mobile,Android,SESS-019,https://site.com/cart,Cart,update,31,340,234,SVR-118,El Paso,US-South,Semi-structured,0.24,SSD,2.6,JSON,2024-03-01,BATCH-004,Mobile_App,15,390,NULL,0,96,Node-A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>BD-020,2024-03-01 00:00:20,USR-10020,Memphis,Tablet,iOS,SESS-020,https://site.com/checkout,Checkout,purchase,92,1560,789,SVR-119,Memphis,US-South,Structured,0.83,SSD,3.6,Parquet,2024-03-01,BATCH-004,Web_Log,32,620,NULL,0,98,Node-A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>BD-021,2024-03-01 00:00:21,USR-10021,Boston,Desktop,Windows,SESS-021,https://site.com/home,Homepage,view,44,1050,345,SVR-120,Boston,US-East,Structured,0.49,SSD,3.0,Parquet,2024-03-01,BATCH-004,Web_Log,21,440,NULL,0,97,Node-A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>BD-022,2024-03-01 00:00:22,USR-10022,Seattle,Mobile,Android,SESS-022,https://site.com/product,Product,review,67,890,456,SVR-121,Seattle,US-West,Semi-structured,0.58,SSD,3.2,JSON,2024-03-01,BATCH-004,Mobile_App,24,480,NULL,0,99,Node-A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>BD-023,2024-03-01 00:00:23,USR-10023,Denver,Desktop,Linux,SESS-023,https://site.com/search,Search,search,14,560,289,SVR-122,Denver,US-Central,Structured,0.29,HDD,1.7,Avro,2024-03-01,BATCH-004,Web_Log,18,350,NULL,0,90,Node-A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>BD-024,2024-03-01 00:00:24,USR-10024,Baltimore,Tablet,iOS,SESS-024,https://site.com/cart,Cart,view,25,190,145,SVR-123,Baltimore,US-East,Semi-structured,0.16,SSD,2.3,JSON,2024-03-01,BATCH-005,Mobile_App,10,260,NULL,0,93,Node-A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>BD-025,2024-03-01 00:00:25,USR-10025,Nashville,Mobile,iOS,SESS-025,https://site.com/checkout,Checkout,purchase,78,1340,678,SVR-124,Nashville,US-South,Structured,0.72,SSD,3.4,Parquet,2024-03-01,BATCH-005,Web_Log,29,560,NULL,0,98,Node-A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>BD-026,2024-03-01 00:00:26,USR-10026,Portland,Desktop,Windows,SESS-026,https://site.com/home,Homepage,view,41,980,312,SVR-125,Portland,US-West,Structured,0.46,SSD,2.9,Parquet,2024-03-01,BATCH-005,Web_Log,20,430,NULL,0,96,Node-A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>BD-027,2024-03-01 00:00:27,USR-10027,Las Vegas,Mobile,Android,SESS-027,https://site.com/product,Product,click,18,92,134,SVR-126,Las Vegas,US-West,Semi-structured,0.13,SSD,2.4,JSON,2024-03-01,BATCH-005,Mobile_App,8,210,NULL,0,94,Node-A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>BD-028,2024-03-01 00:00:28,USR-10028,Oklahoma City,Tablet,iOS,SESS-028,https://site.com/search,Search,search,11,410,223,SVR-127,Oklahoma City,US-Central,Structured,0.22,HDD,1.9,CSV,2024-03-01,BATCH-005,Web_Log,12,300,403,1,87,Node-A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>BD-029,2024-03-01 00:00:29,USR-10029,Louisville,Desktop,Linux,SESS-029,https://site.com/cart,Cart,add_item,28,670,345,SVR-128,Louisville,US-Central,Structured,0.37,SSD,2.7,Parquet,2024-03-01,BATCH-005,Web_Log,16,410,NULL,0,95,Node-A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>BD-030,2024-03-01 00:00:30,USR-10030,Milwaukee,Mobile,iOS,SESS-030,https://site.com/checkout,Checkout,purchase,71,1120,567,SVR-129,Milwaukee,US-Central,Semi-structured,0.63,SSD,3.1,JSON,2024-03-01,BATCH-006,Mobile_App,26,490,NULL,0,99,Node-A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1031,2024-02-06,2024,February,Q2,CUST-030,Brian Scott,34,Corporate,Texas,Houston,PROD-031,Gaming Headset,Electronics,Audio,119.99,119.99,1,0.05,35.99,12.00,3,Net30,High,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1032,2024-02-06,2024,February,Q2,CUST-031,Carolyn Adams,44,Home Office,New York,Rochester,PROD-032,Night Stand,Furniture,Storage,34.99,69.99,2,0.10,20.99,15.00,3,Net15,Medium,Delivered,FALSE,Carol Martinez,East</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1033,2024-02-07,2024,February,Q2,CUST-032,Frank Baker,29,Consumer,California,San Jose,PROD-033,Athletic Shoes,Clothing,Mens,109.99,109.99,1,0.15,32.99,10.00,2,COD,Medium,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1034,2024-02-07,2024,February,Q2,CUST-033,Ruth Gonzalez,38,Consumer,Missouri,St Louis,PROD-034,Smart Watch,Electronics,Wearables,199.99,199.99,1,0.05,59.99,12.00,3,Net15,High,Delivered,FALSE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1035,2024-02-08,2024,February,Q2,CUST-034,Peter Nelson,31,Corporate,Florida,Tampa,PROD-035,Bluetooth Speaker,Electronics,Audio,39.99,79.99,2,0.10,23.99,10.00,3,Net30,Medium,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1036,2024-02-08,2024,February,Q2,CUST-035,Kimberly Carter,41,Consumer,Pennsylvania,Pittsburgh,PROD-036,Cashmere Sweater,Clothing,Womens,99.99,99.99,1,0.00,29.99,12.00,3,COD,Low,Returned,TRUE,Carol Martinez,East</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1037,2024-02-09,2024,February,Q2,CUST-036,Steven Mitchell,46,Home Office,Oregon,Eugene,PROD-037,Bookshelf,Furniture,Storage,129.99,129.99,1,0.05,38.99,18.00,4,Net15,Medium,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1038,2024-02-09,2024,February,Q2,CUST-037,Laura Perez,28,Consumer,Iowa,Des Moines,PROD-038,Mesh Router,Electronics,Networking,99.99,99.99,1,0.10,29.99,10.00,2,COD,Low,Delivered,FALSE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1039,2024-02-10,2024,February,Q2,CUST-038,Paul Roberts,23,Consumer,Texas,San Antonio,PROD-039,Golf Polo,Clothing,Mens,15.00,44.99,3,0.15,13.49,8.50,2,COD,Medium,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1040,2024-02-10,2024,February,Q2,CUST-039,Mary Turner,43,Corporate,Washington,Spokane,PROD-040,Graphics Card,Electronics,Components,499.99,499.99,1,0.20,149.99,18.00,4,Net30,High,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1041,2024-03-01,2024,March,Q3,CUST-040,Daniel Phillips,50,Corporate,Illinois,Chicago,PROD-041,Desktop PC,Electronics,Computers,999.99,999.99,1,0.05,299.99,25.00,3,Net30,High,Delivered,FALSE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1042,2024-03-01,2024,March,Q3,CUST-041,Lisa Campbell,27,Consumer,Texas,Austin,PROD-042,Yoga Pants,Clothing,Womens,25.00,49.99,2,0.00,14.99,8.50,2,COD,Medium,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1043,2024-03-02,2024,March,Q3,CUST-042,Ronald Parker,55,Corporate,New York,New York,PROD-043,Coffee Table,Furniture,Tables,249.99,249.99,1,0.10,74.99,22.00,4,Net30,High,Delivered,FALSE,Carol Martinez,East</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1044,2024-03-02,2024,March,Q3,CUST-043,Deborah Evans,34,Home Office,California,Los Angeles,PROD-044,Smart Speaker,Electronics,Smart Home,45.00,89.99,2,0.00,26.99,10.00,2,Net15,Medium,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1045,2024-03-03,2024,March,Q3,CUST-044,Joseph Edwards,19,Consumer,Michigan,Detroit,PROD-045,Baseball Cap,Clothing,Accessories,5.00,19.99,4,0.05,5.99,8.50,2,COD,Low,Delivered,FALSE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1046,2024-03-03,2024,March,Q3,CUST-045,Barbara Collins,38,Consumer,Florida,Miami,PROD-046,Quadcopter,Electronics,Drones,349.99,349.99,1,0.10,104.99,18.00,3,COD,High,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1047,2024-03-04,2024,March,Q3,CUST-046,Mark Stewart,42,Consumer,Pennsylvania,Philadelphia,PROD-047,Wall Mirror,Furniture,Decor,30.00,59.99,2,0.00,17.99,12.00,2,COD,Medium,Delivered,FALSE,Carol Martinez,East</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1048,2024-03-04,2024,March,Q3,CUST-047,Carol Morris,35,Home Office,Oregon,Portland,PROD-048,Flannel Shirt,Clothing,Mens,25.00,49.99,2,0.10,14.99,10.00,3,Net15,Medium,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1049,2024-03-05,2024,March,Q3,CUST-048,Raymond Rogers,24,Consumer,Ohio,Columbus,PROD-049,Streaming Stick,Electronics,Streaming,10.00,29.99,3,0.05,8.99,8.50,2,COD,Low,Returned,TRUE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1050,2024-03-05,2024,March,Q3,CUST-049,Anna Reed,22,Consumer,Georgia,Atlanta,PROD-050,Leggings,Clothing,Womens,7.50,29.99,4,0.00,8.99,8.50,2,COD,Medium,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Big Data Overview</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data? Define the 5 Vs of Big Data (Volume, Velocity, Variety, Veracity, Value) using examples from the dataset.</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>Volume: 30+ records in seconds; Velocity: 30 records per 30 seconds; Variety: Structured, Semi-structured, Unstructured data; Veracity: Error codes (404,401,500); Value: Customer purchase patterns</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>The 5 Vs help characterize Big Data challenges and opportunities</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Big Data Overview</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Analyze the 'Volume' aspect: How many records were generated in 30 seconds? What is the data generation rate per second?</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>30 records in 30 seconds = 1 record/second. Extrapolated: 86,400 records/day, 2.6M records/month</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>Big Data volume requires distributed storage and processing systems</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Big Data Overview</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Analyze the 'Velocity' aspect: What is the average processing time? How does this relate to real-time vs batch processing?</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>Average Processing Time: 0.36 seconds. Range: 0.08s to 0.83s. This enables near real-time processing. Batch processing (BATCH-001 to BATCH-006) groups records</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>Different velocity requirements (real-time vs batch) require different architectures</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Big Data Overview</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Analyze the 'Variety' aspect: Identify the different data types in the dataset. What formats are used for storage?</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>Data Types: Structured (CSV, Parquet, Avro), Semi-structured (JSON), Unstructured (Text). This represents the variety challenge</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>Big Data must handle multiple formats; choosing right format impacts performance</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Big Data Overview</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Analyze the 'Veracity' aspect: How many records have errors? What are the error codes? What is the average data quality score?</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>3 records with errors (404,401,500). Error rate: 10%. Average Quality Score: 94.3 (range 85-99)</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>Data quality and trustworthiness are critical; error handling is essential</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Big Data Overview</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Analyze the 'Value' aspect: From the dataset, what business insights can be derived about customer behavior?</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>Purchase actions: highest duration (67-92 sec), highest data size (890-1560 KB). Mobile users more likely to purchase</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>Extracting business value from data is the ultimate goal of Big Data</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Big Data Overview</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between structured, semi-structured, and unstructured data? Provide examples from the dataset.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>Structured: CSV, Parquet, Avro (predictable schema). Semi-structured: JSON (flexible schema). Unstructured: Text (no schema)</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>Understanding data types helps choose appropriate storage and processing</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Big Data Overview</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>What is data compression and why is it important in Big Data? Compare compression ratios in the dataset.</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>Compression ratios range from 1.2 to 3.6. Higher compression (3.6) means less storage but more CPU. SSDs have higher compression than HDDs</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>Compression reduces storage costs but requires processing power</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Big Data Overview</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between batch processing and stream processing? Identify examples from the dataset.</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>Batch: BATCH-001 to BATCH-006 groups records processed together. Stream: Each record has latency (5-32 ms) indicating streaming</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>Batch for large volumes; Stream for real-time insights</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Big Data Overview</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>What is latency and throughput in Big Data systems? Calculate average latency and throughput from the dataset.</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>Average Latency: 16.2 ms (range 5-32 ms). Average Throughput: 379 MBps (range 180-620 MBps)</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>Latency = time to process; Throughput = data processed per second</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Big Data Overview</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>What is data partitioning? Identify the partition key in the dataset. Why is partitioning important?</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>Partition Key: 2024-03-01 (date). Partitions data by date for efficient querying. Also BATCH_ID groups records</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>Partitioning improves query performance and data management</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Big Data Overview</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between HDD and SSD storage? How does storage type affect performance in Big Data?</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>SSD: Faster (0.08-0.83s processing, compression 2.0-3.6). HDD: Slower (0.15-0.52s, compression 1.2-1.9)</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>SSD for hot data (frequent access); HDD for cold data (archival)</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Big Data Overview</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>What is data replication? Why is it important for Big Data reliability? Analyze server distribution.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>Multiple servers across data centers (US-East, West, Central, South). Server IDs SVR-101 to SVR-129 distributed</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>Replication ensures high availability and fault tolerance</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Big Data Overview</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>What are common Big Data file formats? Compare Parquet, JSON, CSV, Avro from the dataset.</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>Parquet: Columnar, high compression (2.2-3.6), structured. JSON: Semi-structured, flexible. CSV: Simple but inefficient. Avro: Row-based, schema evolution</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>Choose format based on use case: analytics vs operational</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Big Data Overview</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>What is the CAP Theorem? How does it apply to distributed Big Data systems? Analyze data center distribution.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>Consistency, Availability, Partition Tolerance. Data centers: US-East, West, Central, South - prioritizing availability and partition tolerance</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>Distributed systems must make trade-offs between consistency, availability, and partition tolerance</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Big Data Overview</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>What are the challenges of processing Big Data at scale? Identify challenges from the dataset metrics.</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>Challenges: Volume (30 records/sec), Velocity (real-time processing), Variety (multiple formats), Errors (10% error rate), Latency (5-32ms)</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>Big Data requires distributed computing frameworks like Hadoop, Spark</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Big Data Overview</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>What is the role of distributed computing in Big Data? How are nodes used in the dataset?</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>Processing Nodes: Node-A1, A2, A3, A4 distributed across data centers. Each node processes different records</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>Distributed computing enables parallel processing of large datasets</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Big Data Overview</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>What are the 3 Vs of Big Data? Provide metrics from the dataset for each.</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>Volume: 30 records/30sec; Velocity: 0.36sec avg processing; Variety: 3 data types, 4 formats</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>The 3 Vs are the core characteristics of Big Data</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Big Data Overview</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between scalability and elasticity in Big Data systems? How does the dataset demonstrate this?</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>Scalability: Adding more nodes (Node-A1 to A4). Elasticity: Dynamic resource allocation based on load (different batch sizes)</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>Scalability = ability to grow; Elasticity = ability to adapt to changing loads</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Big Data Overview</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>What are the key components of a Big Data architecture? Map the dataset fields to architecture components.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>Components: Data Ingestion (Stream_Source), Storage (Storage_Type, Data_Format), Processing (Processing_Time, Processing_Node), Analysis (Data_Quality_Score), Visualization (Action_Type, Page_Category)</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>Modern Big Data architecture includes ingestion, storage, processing, analysis, and visualization layers</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>